--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272032</v>
+        <v>121272047</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319599</v>
+        <v>319546</v>
       </c>
       <c r="R2" t="n">
-        <v>6521493</v>
+        <v>6521443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272047</v>
+        <v>121272028</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319546</v>
+        <v>319646</v>
       </c>
       <c r="R3" t="n">
-        <v>6521443</v>
+        <v>6521558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272029</v>
+        <v>121272032</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319593</v>
+        <v>319599</v>
       </c>
       <c r="R4" t="n">
-        <v>6521547</v>
+        <v>6521493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R5" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272032</v>
+        <v>121272029</v>
       </c>
       <c r="B4" t="n">
         <v>57367</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319599</v>
+        <v>319593</v>
       </c>
       <c r="R4" t="n">
-        <v>6521493</v>
+        <v>6521547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272029</v>
+        <v>121272032</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319593</v>
+        <v>319599</v>
       </c>
       <c r="R5" t="n">
-        <v>6521547</v>
+        <v>6521493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272047</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R3" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272029</v>
+        <v>121272032</v>
       </c>
       <c r="B4" t="n">
         <v>57367</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319593</v>
+        <v>319599</v>
       </c>
       <c r="R4" t="n">
-        <v>6521547</v>
+        <v>6521493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272032</v>
+        <v>121272028</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319599</v>
+        <v>319646</v>
       </c>
       <c r="R5" t="n">
-        <v>6521493</v>
+        <v>6521558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272047</v>
+        <v>121272029</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319546</v>
+        <v>319593</v>
       </c>
       <c r="R2" t="n">
-        <v>6521443</v>
+        <v>6521547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272029</v>
+        <v>121272047</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319593</v>
+        <v>319546</v>
       </c>
       <c r="R3" t="n">
-        <v>6521547</v>
+        <v>6521443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272032</v>
+        <v>121272028</v>
       </c>
       <c r="B4" t="n">
         <v>57367</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319599</v>
+        <v>319646</v>
       </c>
       <c r="R4" t="n">
-        <v>6521493</v>
+        <v>6521558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272028</v>
+        <v>121272032</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319646</v>
+        <v>319599</v>
       </c>
       <c r="R5" t="n">
-        <v>6521558</v>
+        <v>6521493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272029</v>
+        <v>121272032</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319593</v>
+        <v>319599</v>
       </c>
       <c r="R2" t="n">
-        <v>6521547</v>
+        <v>6521493</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>121272047</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R4" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272032</v>
+        <v>121272028</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319599</v>
+        <v>319646</v>
       </c>
       <c r="R5" t="n">
-        <v>6521493</v>
+        <v>6521558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272047</v>
+        <v>121272028</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319546</v>
+        <v>319646</v>
       </c>
       <c r="R3" t="n">
-        <v>6521443</v>
+        <v>6521558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272029</v>
+        <v>121272047</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319593</v>
+        <v>319546</v>
       </c>
       <c r="R4" t="n">
-        <v>6521547</v>
+        <v>6521443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B5" t="n">
         <v>57370</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R5" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272032</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R3" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272047</v>
+        <v>121272028</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319546</v>
+        <v>319646</v>
       </c>
       <c r="R4" t="n">
-        <v>6521443</v>
+        <v>6521558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272029</v>
+        <v>121272047</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>91995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319593</v>
+        <v>319546</v>
       </c>
       <c r="R5" t="n">
-        <v>6521547</v>
+        <v>6521443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272032</v>
+        <v>121272028</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319599</v>
+        <v>319646</v>
       </c>
       <c r="R2" t="n">
-        <v>6521493</v>
+        <v>6521558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>121272029</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272028</v>
+        <v>121272047</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319646</v>
+        <v>319546</v>
       </c>
       <c r="R4" t="n">
-        <v>6521558</v>
+        <v>6521443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272047</v>
+        <v>121272032</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319546</v>
+        <v>319599</v>
       </c>
       <c r="R5" t="n">
-        <v>6521443</v>
+        <v>6521493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272028</v>
+        <v>121272047</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319646</v>
+        <v>319546</v>
       </c>
       <c r="R2" t="n">
-        <v>6521558</v>
+        <v>6521443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272029</v>
+        <v>121272032</v>
       </c>
       <c r="B3" t="n">
         <v>57372</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319593</v>
+        <v>319599</v>
       </c>
       <c r="R3" t="n">
-        <v>6521547</v>
+        <v>6521493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272047</v>
+        <v>121272029</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319546</v>
+        <v>319593</v>
       </c>
       <c r="R4" t="n">
-        <v>6521443</v>
+        <v>6521547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272032</v>
+        <v>121272028</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319599</v>
+        <v>319646</v>
       </c>
       <c r="R5" t="n">
-        <v>6521493</v>
+        <v>6521558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272047</v>
+        <v>121272028</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319546</v>
+        <v>319646</v>
       </c>
       <c r="R2" t="n">
-        <v>6521443</v>
+        <v>6521558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272029</v>
+        <v>121272047</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319593</v>
+        <v>319546</v>
       </c>
       <c r="R4" t="n">
-        <v>6521547</v>
+        <v>6521443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272028</v>
+        <v>121272029</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319646</v>
+        <v>319593</v>
       </c>
       <c r="R5" t="n">
-        <v>6521558</v>
+        <v>6521547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2185-2022 artfynd.xlsx
+++ b/artfynd/A 2185-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272028</v>
+        <v>121272032</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319646</v>
+        <v>319599</v>
       </c>
       <c r="R2" t="n">
-        <v>6521558</v>
+        <v>6521493</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272032</v>
+        <v>121272029</v>
       </c>
       <c r="B3" t="n">
         <v>57372</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319599</v>
+        <v>319593</v>
       </c>
       <c r="R3" t="n">
-        <v>6521493</v>
+        <v>6521547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272029</v>
+        <v>121272028</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>319593</v>
+        <v>319646</v>
       </c>
       <c r="R5" t="n">
-        <v>6521547</v>
+        <v>6521558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
